--- a/Base_hdc_copa.xlsx
+++ b/Base_hdc_copa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victor.falcao_tembic\Documents\copa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145019A0-58E4-4AAD-9340-17B2E5C0B425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3FDDB3-FF4D-45CB-AC9C-94648D93C29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-5250" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4863,7 +4863,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="27.86328125" customWidth="1"/>
-    <col min="2" max="2" width="17.2265625" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -4886,7 +4886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>9</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>386</v>
+        <v>9</v>
       </c>
     </row>
     <row r="506" spans="1:6" ht="13" x14ac:dyDescent="0.6">

--- a/Base_hdc_copa.xlsx
+++ b/Base_hdc_copa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victor.falcao_tembic\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D101B053-ED7C-4FA2-BA34-3CA2E767D16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CEF6F7-597C-4688-A41B-5CC8F232DA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-5250" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4607" uniqueCount="1562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4608" uniqueCount="1564">
   <si>
     <t>e-mail</t>
   </si>
@@ -4502,9 +4502,6 @@
     <t>jhon.rodriguez</t>
   </si>
   <si>
-    <t xml:space="preserve">ticket de creacion </t>
-  </si>
-  <si>
     <t>guilherme.monteiro@tembici.com</t>
   </si>
   <si>
@@ -4725,13 +4722,22 @@
   </si>
   <si>
     <t>CD Extrema</t>
+  </si>
+  <si>
+    <t>christian.castro.gigroup@tembici-consult.com</t>
+  </si>
+  <si>
+    <t>christian.castro</t>
+  </si>
+  <si>
+    <t>camilo.polania</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4758,6 +4764,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4780,7 +4793,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4795,6 +4808,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6135,7 +6151,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>10</v>
@@ -8826,10 +8842,10 @@
     </row>
     <row r="191" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A191" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>8</v>
@@ -8846,10 +8862,10 @@
     </row>
     <row r="192" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A192" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>8</v>
@@ -8866,10 +8882,10 @@
     </row>
     <row r="193" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A193" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>8</v>
@@ -8926,10 +8942,10 @@
     </row>
     <row r="196" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A196" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>8</v>
@@ -8966,10 +8982,10 @@
     </row>
     <row r="198" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A198" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>8</v>
@@ -8981,15 +8997,15 @@
         <v>31</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A199" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>8</v>
@@ -9026,10 +9042,10 @@
     </row>
     <row r="201" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A201" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>8</v>
@@ -13566,10 +13582,10 @@
     </row>
     <row r="428" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A428" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>8</v>
@@ -16026,10 +16042,10 @@
     </row>
     <row r="551" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A551" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>8</v>
@@ -16046,10 +16062,10 @@
     </row>
     <row r="552" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A552" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>8</v>
@@ -16066,10 +16082,10 @@
     </row>
     <row r="553" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A553" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>8</v>
@@ -16086,10 +16102,10 @@
     </row>
     <row r="554" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A554" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>8</v>
@@ -16106,10 +16122,10 @@
     </row>
     <row r="555" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A555" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>8</v>
@@ -16126,10 +16142,10 @@
     </row>
     <row r="556" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A556" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>8</v>
@@ -16146,10 +16162,10 @@
     </row>
     <row r="557" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A557" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>8</v>
@@ -16166,10 +16182,10 @@
     </row>
     <row r="558" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A558" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>8</v>
@@ -16186,10 +16202,10 @@
     </row>
     <row r="559" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A559" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>8</v>
@@ -16206,10 +16222,10 @@
     </row>
     <row r="560" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A560" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>8</v>
@@ -16226,10 +16242,10 @@
     </row>
     <row r="561" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A561" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>8</v>
@@ -16246,10 +16262,10 @@
     </row>
     <row r="562" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A562" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>8</v>
@@ -16266,10 +16282,10 @@
     </row>
     <row r="563" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A563" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>8</v>
@@ -16286,10 +16302,10 @@
     </row>
     <row r="564" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A564" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>8</v>
@@ -16306,10 +16322,10 @@
     </row>
     <row r="565" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A565" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>8</v>
@@ -16326,10 +16342,10 @@
     </row>
     <row r="566" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A566" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>8</v>
@@ -16346,10 +16362,10 @@
     </row>
     <row r="567" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A567" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>8</v>
@@ -16366,10 +16382,10 @@
     </row>
     <row r="568" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A568" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>8</v>
@@ -16441,7 +16457,7 @@
         <v>31</v>
       </c>
       <c r="F571" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="572" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16461,7 +16477,7 @@
         <v>31</v>
       </c>
       <c r="F572" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="573" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16481,7 +16497,7 @@
         <v>31</v>
       </c>
       <c r="F573" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="574" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16501,7 +16517,7 @@
         <v>31</v>
       </c>
       <c r="F574" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="575" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16521,7 +16537,7 @@
         <v>31</v>
       </c>
       <c r="F575" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="576" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16541,7 +16557,7 @@
         <v>31</v>
       </c>
       <c r="F576" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="577" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16561,15 +16577,15 @@
         <v>31</v>
       </c>
       <c r="F577" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="578" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A578" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>8</v>
@@ -16581,15 +16597,15 @@
         <v>31</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="579" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A579" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>8</v>
@@ -16601,15 +16617,15 @@
         <v>31</v>
       </c>
       <c r="F579" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="580" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A580" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>8</v>
@@ -16621,15 +16637,15 @@
         <v>31</v>
       </c>
       <c r="F580" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="581" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A581" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>8</v>
@@ -16641,7 +16657,7 @@
         <v>31</v>
       </c>
       <c r="F581" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="582" spans="1:6" ht="13" x14ac:dyDescent="0.6">
@@ -16926,10 +16942,10 @@
     </row>
     <row r="596" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A596" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>1126</v>
@@ -17146,10 +17162,10 @@
     </row>
     <row r="607" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A607" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>1126</v>
@@ -18466,10 +18482,10 @@
     </row>
     <row r="673" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A673" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>1126</v>
@@ -18646,10 +18662,10 @@
     </row>
     <row r="682" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A682" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>1126</v>
@@ -18666,10 +18682,10 @@
     </row>
     <row r="683" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A683" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>1126</v>
@@ -18826,10 +18842,10 @@
     </row>
     <row r="691" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A691" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>1324</v>
@@ -18866,10 +18882,10 @@
     </row>
     <row r="693" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A693" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>1324</v>
@@ -20228,8 +20244,8 @@
       <c r="A761" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="B761" s="3" t="s">
-        <v>1474</v>
+      <c r="B761" s="6" t="s">
+        <v>1563</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>1408</v>
@@ -20366,7 +20382,10 @@
     </row>
     <row r="768" spans="1:6" ht="13" x14ac:dyDescent="0.6">
       <c r="A768" s="1" t="s">
-        <v>1487</v>
+        <v>1561</v>
+      </c>
+      <c r="B768" s="6" t="s">
+        <v>1562</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>1408</v>

--- a/Base_hdc_copa.xlsx
+++ b/Base_hdc_copa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victor.falcao_tembic\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victor.falcao_tembic\Documents\copa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CEF6F7-597C-4688-A41B-5CC8F232DA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB62119-4645-4B0B-BC71-5421F8BBD85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-5250" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4608" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4836" uniqueCount="1638">
   <si>
     <t>e-mail</t>
   </si>
@@ -4731,6 +4731,228 @@
   </si>
   <si>
     <t>camilo.polania</t>
+  </si>
+  <si>
+    <t>rafael.fazzolino@tembici.com</t>
+  </si>
+  <si>
+    <t>rafael.fazzolino</t>
+  </si>
+  <si>
+    <t>adriano.bpereira@tembici.com</t>
+  </si>
+  <si>
+    <t>alisson.oliveira@tembici.com</t>
+  </si>
+  <si>
+    <t>arthur.moreira@tembici.com</t>
+  </si>
+  <si>
+    <t>fernanda.silva@tembici.com</t>
+  </si>
+  <si>
+    <t>jefte.nascimento@tembici.com</t>
+  </si>
+  <si>
+    <t>juliana.pereira@tembici.com</t>
+  </si>
+  <si>
+    <t>kevin.mesquita@tembici.com</t>
+  </si>
+  <si>
+    <t>melissa.souza@tembici.com</t>
+  </si>
+  <si>
+    <t>ramon.leal@tembici.com</t>
+  </si>
+  <si>
+    <t>ronaldronald.santos@tembici.com</t>
+  </si>
+  <si>
+    <t>sergio.rocha@tembici.com</t>
+  </si>
+  <si>
+    <t>taiani.silva@tembici.com</t>
+  </si>
+  <si>
+    <t>tiago.paz@tembici.com</t>
+  </si>
+  <si>
+    <t>vanessa.evangelista@tembici.com</t>
+  </si>
+  <si>
+    <t>alex.barros@tembici.com</t>
+  </si>
+  <si>
+    <t>carlos.mendes@tembici.com</t>
+  </si>
+  <si>
+    <t>dieccica.cruz@tembici.com</t>
+  </si>
+  <si>
+    <t>gabriel.jacinto@tembici.com</t>
+  </si>
+  <si>
+    <t>hayde.machado@tembici.com</t>
+  </si>
+  <si>
+    <t>isaias.alves@tembici.com</t>
+  </si>
+  <si>
+    <t>lucas.pinto@tembici.com</t>
+  </si>
+  <si>
+    <t>ricardo.jesus@tembici.com</t>
+  </si>
+  <si>
+    <t>thauan.nascimento@tembici.com</t>
+  </si>
+  <si>
+    <t>angelo.perossi@tembici.com</t>
+  </si>
+  <si>
+    <t>caroline.maldonado@tembici.com</t>
+  </si>
+  <si>
+    <t>fabiana.candida@tembici.com</t>
+  </si>
+  <si>
+    <t>jamile.jesus@tembici.com</t>
+  </si>
+  <si>
+    <t>joao.braga.terceiro@tembici-consult.com</t>
+  </si>
+  <si>
+    <t>luiz.araujo@tembici.com</t>
+  </si>
+  <si>
+    <t>luis.tavares@tembici.com</t>
+  </si>
+  <si>
+    <t>marcos.barros@tembici.com</t>
+  </si>
+  <si>
+    <t>matheus.assis@tembici.com</t>
+  </si>
+  <si>
+    <t>miguel.figueiredo@tembici.com</t>
+  </si>
+  <si>
+    <t>oziel.caetano@tembici.com</t>
+  </si>
+  <si>
+    <t>petherson.pinto@tembici.com</t>
+  </si>
+  <si>
+    <t>luisa.romero@tembici.com</t>
+  </si>
+  <si>
+    <t>adriano.bpereira</t>
+  </si>
+  <si>
+    <t>alisson.oliveira</t>
+  </si>
+  <si>
+    <t>arthur.moreira</t>
+  </si>
+  <si>
+    <t>fernanda.silva</t>
+  </si>
+  <si>
+    <t>jefte.nascimento</t>
+  </si>
+  <si>
+    <t>juliana.pereira</t>
+  </si>
+  <si>
+    <t>kevin.mesquita</t>
+  </si>
+  <si>
+    <t>melissa.souza</t>
+  </si>
+  <si>
+    <t>ramon.leal</t>
+  </si>
+  <si>
+    <t>ronaldronald.santos</t>
+  </si>
+  <si>
+    <t>sergio.rocha</t>
+  </si>
+  <si>
+    <t>taiani.silva</t>
+  </si>
+  <si>
+    <t>tiago.paz</t>
+  </si>
+  <si>
+    <t>vanessa.evangelista</t>
+  </si>
+  <si>
+    <t>alex.barros</t>
+  </si>
+  <si>
+    <t>carlos.mendes</t>
+  </si>
+  <si>
+    <t>dieccica.cruz</t>
+  </si>
+  <si>
+    <t>gabriel.jacinto</t>
+  </si>
+  <si>
+    <t>hayde.machado</t>
+  </si>
+  <si>
+    <t>isaias.alves</t>
+  </si>
+  <si>
+    <t>lucas.pinto</t>
+  </si>
+  <si>
+    <t>ricardo.jesus</t>
+  </si>
+  <si>
+    <t>thauan.nascimento</t>
+  </si>
+  <si>
+    <t>angelo.perossi</t>
+  </si>
+  <si>
+    <t>caroline.maldonado</t>
+  </si>
+  <si>
+    <t>fabiana.candida</t>
+  </si>
+  <si>
+    <t>jamile.jesus</t>
+  </si>
+  <si>
+    <t>luiz.araujo</t>
+  </si>
+  <si>
+    <t>luis.tavares</t>
+  </si>
+  <si>
+    <t>marcos.barros</t>
+  </si>
+  <si>
+    <t>matheus.assis</t>
+  </si>
+  <si>
+    <t>miguel.figueiredo</t>
+  </si>
+  <si>
+    <t>oziel.caetano</t>
+  </si>
+  <si>
+    <t>petherson.pinto</t>
+  </si>
+  <si>
+    <t>luisa.romero</t>
+  </si>
+  <si>
+    <t>joao.braga.terceiro</t>
   </si>
 </sst>
 </file>
@@ -4793,7 +5015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4803,9 +5025,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5032,7 +5251,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F769"/>
+  <dimension ref="A1:F806"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="44.40625" style="3" customWidth="1"/>
@@ -5436,7 +5655,7 @@
       <c r="E20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6876,7 +7095,7 @@
       <c r="E92" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19881,7 +20100,7 @@
       </c>
     </row>
     <row r="743" spans="1:6" ht="13" x14ac:dyDescent="0.6">
-      <c r="A743" s="4" t="s">
+      <c r="A743" s="2" t="s">
         <v>1438</v>
       </c>
       <c r="B743" s="3" t="s">
@@ -20244,7 +20463,7 @@
       <c r="A761" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="B761" s="6" t="s">
+      <c r="B761" s="5" t="s">
         <v>1563</v>
       </c>
       <c r="C761" s="2" t="s">
@@ -20384,7 +20603,7 @@
       <c r="A768" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="B768" s="6" t="s">
+      <c r="B768" s="5" t="s">
         <v>1562</v>
       </c>
       <c r="C768" s="2" t="s">
@@ -20400,11 +20619,765 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="769" spans="3:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="C769" s="2"/>
-      <c r="D769" s="2"/>
-      <c r="E769" s="2"/>
-      <c r="F769" s="2"/>
+    <row r="769" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A769" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B769" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C769" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D769" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E769" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F769" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A770" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B770" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C770" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D770" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E770" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F770" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A771" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B771" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C771" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D771" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E771" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F771" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A772" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B772" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C772" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D772" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E772" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F772" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A773" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B773" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C773" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D773" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E773" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F773" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A774" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B774" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C774" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D774" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E774" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F774" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A775" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B775" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C775" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D775" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E775" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F775" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A776" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B776" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C776" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D776" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E776" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F776" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A777" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B777" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C777" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D777" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E777" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F777" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A778" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B778" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C778" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D778" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E778" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F778" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A779" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B779" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C779" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D779" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E779" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F779" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A780" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B780" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C780" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D780" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E780" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F780" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A781" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B781" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C781" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D781" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E781" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F781" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A782" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B782" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C782" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D782" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E782" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F782" s="5" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A783" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B783" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C783" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D783" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E783" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F783" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A784" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B784" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C784" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D784" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E784" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F784" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A785" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B785" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C785" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D785" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E785" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F785" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A786" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B786" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C786" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D786" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E786" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F786" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A787" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B787" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C787" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D787" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E787" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F787" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A788" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B788" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C788" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D788" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E788" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F788" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A789" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B789" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C789" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D789" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E789" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F789" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A790" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B790" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C790" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D790" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E790" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F790" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A791" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B791" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C791" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D791" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E791" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F791" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A792" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B792" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C792" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D792" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E792" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F792" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A793" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B793" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C793" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D793" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E793" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F793" s="5" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A794" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B794" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C794" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D794" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E794" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F794" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A795" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B795" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C795" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D795" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E795" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F795" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A796" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B796" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C796" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D796" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E796" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F796" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A797" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B797" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C797" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D797" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E797" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F797" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A798" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B798" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C798" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D798" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E798" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F798" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A799" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B799" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C799" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D799" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E799" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F799" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A800" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B800" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C800" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D800" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E800" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F800" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A801" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B801" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C801" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D801" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E801" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F801" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A802" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B802" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C802" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D802" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E802" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F802" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A803" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B803" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C803" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D803" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E803" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F803" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A804" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B804" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C804" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D804" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E804" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F804" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A805" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B805" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C805" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D805" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E805" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F805" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6" ht="13" x14ac:dyDescent="0.6">
+      <c r="A806" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B806" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C806" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D806" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E806" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F806" s="2" t="s">
+        <v>1409</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F768" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -20412,5 +21385,6 @@
     <hyperlink ref="A743" r:id="rId1" xr:uid="{534DA919-E113-4FC1-BC9E-874C89A01E7F}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" copies="2" r:id="rId2"/>
 </worksheet>
 </file>